--- a/DB/LambdaDaCollegare.xlsx
+++ b/DB/LambdaDaCollegare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amedeo\fuse-angular\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF13D324-FCA1-415E-B708-1224A1D7B357}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1413731-3276-4AFF-AC9C-D172010CFBF7}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{467DAA7B-A998-42A6-A092-5B259364BEAC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Lambda da collegare</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>Menù</t>
-  </si>
-  <si>
-    <t>Pre</t>
   </si>
   <si>
     <t>Presidi</t>
@@ -410,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEA87F2-C037-4025-8434-F4F94CA5EF73}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -425,7 +422,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -440,21 +437,16 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
